--- a/Data_with_references.xlsx
+++ b/Data_with_references.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12650" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="3" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -806,9 +806,6 @@
     <t>benzoate</t>
   </si>
   <si>
-    <t>c1cccc1C(=O)[O-]</t>
-  </si>
-  <si>
     <t>cinnamate</t>
   </si>
   <si>
@@ -831,9 +828,6 @@
   </si>
   <si>
     <t>Salicylate</t>
-  </si>
-  <si>
-    <t>c1ccc(O)c1C(=O)[O-]</t>
   </si>
   <si>
     <t>Ito T. H. et al. Molecular variations in aromatic cosolutes: critical role in the rheology of cationic wormlike micelles //Langmuir. – 2014. – Т. 30. – №. 39. – С. 11535-11542.</t>
@@ -944,12 +938,18 @@
   </si>
   <si>
     <t>Hao L. S. et al. Triple-stimuli-responsive hydrogels based on an aqueous mixed sodium stearate and cetyltrimethylammonium bromide system //Journal of Molecular Liquids. – 2022. – Т. 364. – С. 120010.</t>
+  </si>
+  <si>
+    <t>c1ccccc1C(=O)[O-]</t>
+  </si>
+  <si>
+    <t>c1cccc(O)c1C(=O)[O-]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0000"/>
   </numFmts>
@@ -1026,7 +1026,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1305,12 +1305,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" customWidth="1"/>
+    <col min="1" max="1" width="10.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>115</v>
       </c>
@@ -1318,7 +1318,7 @@
         <v>364.45</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3">
         <f>1000*(1000*0.01)/B1</f>
         <v>27.438606118809165</v>
@@ -1327,7 +1327,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>120</v>
       </c>
@@ -1335,7 +1335,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>0.1</v>
       </c>
@@ -1344,7 +1344,7 @@
         <v>4.4642857142857144</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>0.2</v>
       </c>
@@ -1353,7 +1353,7 @@
         <v>8.9285714285714288</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>0.3</v>
       </c>
@@ -1362,7 +1362,7 @@
         <v>13.392857142857142</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>0.35</v>
       </c>
@@ -1379,12 +1379,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1">
         <v>302.92090804548701</v>
       </c>
@@ -1396,7 +1396,7 @@
         <v>241487.88800838901</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>302.92729673324999</v>
       </c>
@@ -1408,7 +1408,7 @@
         <v>141366.699530613</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>302.93837045870703</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>55880.915436266907</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>303.05975552621402</v>
       </c>
@@ -1432,7 +1432,7 @@
         <v>21322.938524639198</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>302.97244346011303</v>
       </c>
@@ -1444,7 +1444,7 @@
         <v>3213.7068680277603</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>303.73866007921902</v>
       </c>
@@ -1456,7 +1456,7 @@
         <v>41.373410807913601</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>304.05085395459702</v>
       </c>
@@ -1476,19 +1476,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J606"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="34.140625" customWidth="1"/>
-    <col min="2" max="2" width="48.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34.1796875" customWidth="1"/>
+    <col min="2" max="2" width="48.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="23.140625" customWidth="1"/>
-    <col min="6" max="6" width="28.85546875" customWidth="1"/>
-    <col min="7" max="7" width="25.5703125" customWidth="1"/>
-    <col min="8" max="9" width="28.28515625" customWidth="1"/>
-    <col min="10" max="10" width="50.28515625" customWidth="1"/>
+    <col min="4" max="5" width="23.1796875" customWidth="1"/>
+    <col min="6" max="6" width="28.81640625" customWidth="1"/>
+    <col min="7" max="7" width="25.54296875" customWidth="1"/>
+    <col min="8" max="9" width="28.26953125" customWidth="1"/>
+    <col min="10" max="10" width="50.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -1520,7 +1520,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>60</v>
       </c>
@@ -1550,7 +1550,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>60</v>
       </c>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="J3" s="7"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>60</v>
       </c>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="J4" s="7"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>60</v>
       </c>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="J5" s="7"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>60</v>
       </c>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="J6" s="7"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>60</v>
       </c>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="J7" s="7"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>60</v>
       </c>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="J8" s="7"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>60</v>
       </c>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="J9" s="7"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>60</v>
       </c>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="J10" s="7"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>60</v>
       </c>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>60</v>
       </c>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="J12" s="7"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>60</v>
       </c>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="J13" s="7"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>60</v>
       </c>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="J14" s="7"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>60</v>
       </c>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="J15" s="7"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>60</v>
       </c>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="J16" s="7"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>60</v>
       </c>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="J17" s="7"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>10</v>
       </c>
@@ -2000,7 +2000,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>10</v>
       </c>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J19" s="7"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="J20" s="7"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>10</v>
       </c>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="J21" s="7"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>10</v>
       </c>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="J22" s="7"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>10</v>
       </c>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="J23" s="7"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>11</v>
       </c>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="J24" s="7"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>11</v>
       </c>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="J25" s="7"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>11</v>
       </c>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="J26" s="7"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>12</v>
       </c>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="J27" s="7"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>12</v>
       </c>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="J28" s="7"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>12</v>
       </c>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="J29" s="7"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>13</v>
       </c>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="J30" s="7"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>13</v>
       </c>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="J31" s="7"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>13</v>
       </c>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="J32" s="7"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>13</v>
       </c>
@@ -2420,7 +2420,7 @@
       </c>
       <c r="J33" s="7"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>13</v>
       </c>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="J34" s="7"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>15</v>
       </c>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="J35" s="7"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>16</v>
       </c>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="J36" s="7"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>17</v>
       </c>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="J37" s="7"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>18</v>
       </c>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="J38" s="7"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>19</v>
       </c>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="J39" s="7"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>20</v>
       </c>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="J40" s="7"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>21</v>
       </c>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="J41" s="7"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>22</v>
       </c>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="J42" s="7"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>23</v>
       </c>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="J43" s="7"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>37</v>
       </c>
@@ -2733,7 +2733,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>37</v>
       </c>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="J45" s="7"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>37</v>
       </c>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="J46" s="7"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>37</v>
       </c>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="J47" s="7"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>37</v>
       </c>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="J48" s="7"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>37</v>
       </c>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="J49" s="7"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>37</v>
       </c>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="J50" s="7"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>37</v>
       </c>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="J51" s="7"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>39</v>
       </c>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="J52" s="7"/>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>39</v>
       </c>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="J53" s="7"/>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>39</v>
       </c>
@@ -3043,7 +3043,7 @@
       </c>
       <c r="J54" s="7"/>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>39</v>
       </c>
@@ -3074,7 +3074,7 @@
       </c>
       <c r="J55" s="7"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>39</v>
       </c>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="J56" s="7"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>39</v>
       </c>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="J57" s="7"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>39</v>
       </c>
@@ -3167,7 +3167,7 @@
       </c>
       <c r="J58" s="7"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>39</v>
       </c>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="J59" s="7"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>39</v>
       </c>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="J60" s="7"/>
     </row>
-    <row r="61" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
         <v>39</v>
       </c>
@@ -3260,7 +3260,7 @@
       </c>
       <c r="J61" s="7"/>
     </row>
-    <row r="62" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
         <v>44</v>
       </c>
@@ -3292,7 +3292,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
         <v>44</v>
       </c>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="J63" s="7"/>
     </row>
-    <row r="64" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
         <v>44</v>
       </c>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="J64" s="7"/>
     </row>
-    <row r="65" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
         <v>62</v>
       </c>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="J65" s="7"/>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>62</v>
       </c>
@@ -3414,7 +3414,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>46</v>
       </c>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="J67" s="7"/>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>46</v>
       </c>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="J68" s="7"/>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>46</v>
       </c>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="J69" s="7"/>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>48</v>
       </c>
@@ -3538,7 +3538,7 @@
       </c>
       <c r="J70" s="7"/>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>48</v>
       </c>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="J71" s="7"/>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>48</v>
       </c>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="J72" s="7"/>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>48</v>
       </c>
@@ -3631,7 +3631,7 @@
       </c>
       <c r="J73" s="7"/>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>48</v>
       </c>
@@ -3662,7 +3662,7 @@
       </c>
       <c r="J74" s="7"/>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>50</v>
       </c>
@@ -3693,7 +3693,7 @@
       </c>
       <c r="J75" s="7"/>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>50</v>
       </c>
@@ -3724,7 +3724,7 @@
       </c>
       <c r="J76" s="7"/>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>50</v>
       </c>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="J77" s="7"/>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>50</v>
       </c>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="J78" s="7"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>50</v>
       </c>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="J79" s="7"/>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>50</v>
       </c>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="J80" s="7"/>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>46</v>
       </c>
@@ -3879,7 +3879,7 @@
       </c>
       <c r="J81" s="7"/>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>46</v>
       </c>
@@ -3910,7 +3910,7 @@
       </c>
       <c r="J82" s="7"/>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>46</v>
       </c>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="J83" s="7"/>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>48</v>
       </c>
@@ -3972,7 +3972,7 @@
       </c>
       <c r="J84" s="7"/>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>48</v>
       </c>
@@ -4003,7 +4003,7 @@
       </c>
       <c r="J85" s="7"/>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>48</v>
       </c>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="J86" s="7"/>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>50</v>
       </c>
@@ -4065,7 +4065,7 @@
       </c>
       <c r="J87" s="7"/>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>50</v>
       </c>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="J88" s="7"/>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>50</v>
       </c>
@@ -4127,7 +4127,7 @@
       </c>
       <c r="J89" s="7"/>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>46</v>
       </c>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="J90" s="7"/>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>48</v>
       </c>
@@ -4189,7 +4189,7 @@
       </c>
       <c r="J91" s="7"/>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>50</v>
       </c>
@@ -4220,7 +4220,7 @@
       </c>
       <c r="J92" s="7"/>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>53</v>
       </c>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="J93" s="7"/>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>53</v>
       </c>
@@ -4284,7 +4284,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>53</v>
       </c>
@@ -4315,7 +4315,7 @@
       </c>
       <c r="J95" s="8"/>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>53</v>
       </c>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="J96" s="8"/>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>53</v>
       </c>
@@ -4377,7 +4377,7 @@
       </c>
       <c r="J97" s="8"/>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>53</v>
       </c>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="J98" s="8"/>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>53</v>
       </c>
@@ -4439,7 +4439,7 @@
       </c>
       <c r="J99" s="8"/>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>68</v>
       </c>
@@ -4471,7 +4471,7 @@
       </c>
       <c r="J100" s="8"/>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>68</v>
       </c>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="J101" s="8"/>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>68</v>
       </c>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="J102" s="8"/>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>68</v>
       </c>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="J103" s="8"/>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>68</v>
       </c>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="J104" s="8"/>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>68</v>
       </c>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="J105" s="8"/>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>58</v>
       </c>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="J106" s="8"/>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>58</v>
       </c>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="J107" s="8"/>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>58</v>
       </c>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="J108" s="8"/>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>69</v>
       </c>
@@ -4743,7 +4743,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>69</v>
       </c>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="J110" s="7"/>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>69</v>
       </c>
@@ -4801,7 +4801,7 @@
       </c>
       <c r="J111" s="7"/>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>69</v>
       </c>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="J112" s="7"/>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>71</v>
       </c>
@@ -4859,7 +4859,7 @@
       </c>
       <c r="J113" s="7"/>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>71</v>
       </c>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="J114" s="7"/>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>71</v>
       </c>
@@ -4917,7 +4917,7 @@
       </c>
       <c r="J115" s="7"/>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>71</v>
       </c>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="J116" s="7"/>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>73</v>
       </c>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="J117" s="7"/>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>73</v>
       </c>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="J118" s="7"/>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>76</v>
       </c>
@@ -5034,7 +5034,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>77</v>
       </c>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="J120" s="7"/>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>80</v>
       </c>
@@ -5091,7 +5091,7 @@
       </c>
       <c r="J121" s="7"/>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>82</v>
       </c>
@@ -5118,7 +5118,7 @@
       </c>
       <c r="J122" s="7"/>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>84</v>
       </c>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="J123" s="7"/>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>56</v>
       </c>
@@ -5176,7 +5176,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>56</v>
       </c>
@@ -5205,7 +5205,7 @@
       </c>
       <c r="J125" s="7"/>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>56</v>
       </c>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="J126" s="7"/>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>56</v>
       </c>
@@ -5263,7 +5263,7 @@
       </c>
       <c r="J127" s="7"/>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>56</v>
       </c>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="J128" s="7"/>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>86</v>
       </c>
@@ -5321,7 +5321,7 @@
       </c>
       <c r="J129" s="7"/>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>86</v>
       </c>
@@ -5350,7 +5350,7 @@
       </c>
       <c r="J130" s="7"/>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>86</v>
       </c>
@@ -5379,7 +5379,7 @@
       </c>
       <c r="J131" s="7"/>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>86</v>
       </c>
@@ -5408,7 +5408,7 @@
       </c>
       <c r="J132" s="7"/>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>88</v>
       </c>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="J133" s="7"/>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>88</v>
       </c>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="J134" s="7"/>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>88</v>
       </c>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="J135" s="7"/>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>88</v>
       </c>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="J136" s="7"/>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>90</v>
       </c>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="J137" s="7"/>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>90</v>
       </c>
@@ -5582,7 +5582,7 @@
       </c>
       <c r="J138" s="7"/>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>90</v>
       </c>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="J139" s="7"/>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>90</v>
       </c>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="J140" s="7"/>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>91</v>
       </c>
@@ -5669,7 +5669,7 @@
       </c>
       <c r="J141" s="7"/>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>91</v>
       </c>
@@ -5698,7 +5698,7 @@
       </c>
       <c r="J142" s="7"/>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>91</v>
       </c>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="J143" s="7"/>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>93</v>
       </c>
@@ -5756,7 +5756,7 @@
       </c>
       <c r="J144" s="7"/>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>93</v>
       </c>
@@ -5785,7 +5785,7 @@
       </c>
       <c r="J145" s="7"/>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>93</v>
       </c>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="J146" s="7"/>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>93</v>
       </c>
@@ -5843,7 +5843,7 @@
       </c>
       <c r="J147" s="7"/>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>95</v>
       </c>
@@ -5872,7 +5872,7 @@
       </c>
       <c r="J148" s="7"/>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>95</v>
       </c>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="J149" s="7"/>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>95</v>
       </c>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="J150" s="7"/>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>95</v>
       </c>
@@ -5959,7 +5959,7 @@
       </c>
       <c r="J151" s="7"/>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>97</v>
       </c>
@@ -5988,7 +5988,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>99</v>
       </c>
@@ -6015,7 +6015,7 @@
       </c>
       <c r="J153" s="8"/>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>102</v>
       </c>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="J154" s="8"/>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>103</v>
       </c>
@@ -6069,7 +6069,7 @@
       </c>
       <c r="J155" s="8"/>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>105</v>
       </c>
@@ -6096,7 +6096,7 @@
       </c>
       <c r="J156" s="8"/>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>107</v>
       </c>
@@ -6123,7 +6123,7 @@
       </c>
       <c r="J157" s="8"/>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>112</v>
       </c>
@@ -6153,7 +6153,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>112</v>
       </c>
@@ -6181,7 +6181,7 @@
       </c>
       <c r="J159" s="7"/>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>112</v>
       </c>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="J160" s="7"/>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>112</v>
       </c>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="J161" s="7"/>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>112</v>
       </c>
@@ -6265,7 +6265,7 @@
       </c>
       <c r="J162" s="7"/>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>112</v>
       </c>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="J163" s="7"/>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>112</v>
       </c>
@@ -6321,7 +6321,7 @@
       </c>
       <c r="J164" s="7"/>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>112</v>
       </c>
@@ -6349,7 +6349,7 @@
       </c>
       <c r="J165" s="7"/>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>112</v>
       </c>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="J166" s="7"/>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>112</v>
       </c>
@@ -6405,7 +6405,7 @@
       </c>
       <c r="J167" s="7"/>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>112</v>
       </c>
@@ -6433,7 +6433,7 @@
       </c>
       <c r="J168" s="7"/>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>112</v>
       </c>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="J169" s="7"/>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>117</v>
       </c>
@@ -6491,7 +6491,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>117</v>
       </c>
@@ -6519,7 +6519,7 @@
       </c>
       <c r="J171" s="8"/>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>117</v>
       </c>
@@ -6547,7 +6547,7 @@
       </c>
       <c r="J172" s="8"/>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>117</v>
       </c>
@@ -6575,7 +6575,7 @@
       </c>
       <c r="J173" s="8"/>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>121</v>
       </c>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="J174" s="8"/>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>122</v>
       </c>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="J175" s="8"/>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>123</v>
       </c>
@@ -6659,7 +6659,7 @@
       </c>
       <c r="J176" s="8"/>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>124</v>
       </c>
@@ -6687,7 +6687,7 @@
       </c>
       <c r="J177" s="8"/>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>128</v>
       </c>
@@ -6715,7 +6715,7 @@
       </c>
       <c r="J178" s="8"/>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>129</v>
       </c>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="J179" s="8"/>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>130</v>
       </c>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="J180" s="8"/>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>131</v>
       </c>
@@ -6799,7 +6799,7 @@
       </c>
       <c r="J181" s="8"/>
     </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>132</v>
       </c>
@@ -6827,7 +6827,7 @@
       </c>
       <c r="J182" s="8"/>
     </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>139</v>
       </c>
@@ -6857,7 +6857,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>139</v>
       </c>
@@ -6885,7 +6885,7 @@
       </c>
       <c r="J184" s="7"/>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>139</v>
       </c>
@@ -6913,7 +6913,7 @@
       </c>
       <c r="J185" s="7"/>
     </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>139</v>
       </c>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="J186" s="7"/>
     </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>139</v>
       </c>
@@ -6969,7 +6969,7 @@
       </c>
       <c r="J187" s="7"/>
     </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>139</v>
       </c>
@@ -6997,7 +6997,7 @@
       </c>
       <c r="J188" s="7"/>
     </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>139</v>
       </c>
@@ -7025,7 +7025,7 @@
       </c>
       <c r="J189" s="7"/>
     </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>139</v>
       </c>
@@ -7053,7 +7053,7 @@
       </c>
       <c r="J190" s="7"/>
     </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>139</v>
       </c>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="J191" s="7"/>
     </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>139</v>
       </c>
@@ -7109,7 +7109,7 @@
       </c>
       <c r="J192" s="7"/>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>139</v>
       </c>
@@ -7137,7 +7137,7 @@
       </c>
       <c r="J193" s="7"/>
     </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>141</v>
       </c>
@@ -7165,7 +7165,7 @@
       </c>
       <c r="J194" s="7"/>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>141</v>
       </c>
@@ -7193,7 +7193,7 @@
       </c>
       <c r="J195" s="7"/>
     </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>141</v>
       </c>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="J196" s="7"/>
     </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>141</v>
       </c>
@@ -7249,7 +7249,7 @@
       </c>
       <c r="J197" s="7"/>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>141</v>
       </c>
@@ -7277,7 +7277,7 @@
       </c>
       <c r="J198" s="7"/>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>141</v>
       </c>
@@ -7305,7 +7305,7 @@
       </c>
       <c r="J199" s="7"/>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>141</v>
       </c>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="J200" s="7"/>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>141</v>
       </c>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="J201" s="7"/>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>141</v>
       </c>
@@ -7389,7 +7389,7 @@
       </c>
       <c r="J202" s="7"/>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>141</v>
       </c>
@@ -7417,7 +7417,7 @@
       </c>
       <c r="J203" s="7"/>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>141</v>
       </c>
@@ -7445,7 +7445,7 @@
       </c>
       <c r="J204" s="7"/>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>141</v>
       </c>
@@ -7473,7 +7473,7 @@
       </c>
       <c r="J205" s="7"/>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>141</v>
       </c>
@@ -7501,7 +7501,7 @@
       </c>
       <c r="J206" s="7"/>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>143</v>
       </c>
@@ -7529,7 +7529,7 @@
       </c>
       <c r="J207" s="7"/>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>143</v>
       </c>
@@ -7557,7 +7557,7 @@
       </c>
       <c r="J208" s="7"/>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>143</v>
       </c>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="J209" s="7"/>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>143</v>
       </c>
@@ -7613,7 +7613,7 @@
       </c>
       <c r="J210" s="7"/>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>143</v>
       </c>
@@ -7641,7 +7641,7 @@
       </c>
       <c r="J211" s="7"/>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>143</v>
       </c>
@@ -7669,7 +7669,7 @@
       </c>
       <c r="J212" s="7"/>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>143</v>
       </c>
@@ -7697,7 +7697,7 @@
       </c>
       <c r="J213" s="7"/>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>143</v>
       </c>
@@ -7725,7 +7725,7 @@
       </c>
       <c r="J214" s="7"/>
     </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>143</v>
       </c>
@@ -7753,7 +7753,7 @@
       </c>
       <c r="J215" s="7"/>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>143</v>
       </c>
@@ -7781,7 +7781,7 @@
       </c>
       <c r="J216" s="7"/>
     </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>143</v>
       </c>
@@ -7809,7 +7809,7 @@
       </c>
       <c r="J217" s="7"/>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>143</v>
       </c>
@@ -7837,7 +7837,7 @@
       </c>
       <c r="J218" s="7"/>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>143</v>
       </c>
@@ -7865,7 +7865,7 @@
       </c>
       <c r="J219" s="7"/>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>143</v>
       </c>
@@ -7893,7 +7893,7 @@
       </c>
       <c r="J220" s="7"/>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>146</v>
       </c>
@@ -7923,7 +7923,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>146</v>
       </c>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="J222" s="7"/>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>146</v>
       </c>
@@ -7979,7 +7979,7 @@
       </c>
       <c r="J223" s="7"/>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>146</v>
       </c>
@@ -8007,7 +8007,7 @@
       </c>
       <c r="J224" s="7"/>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>148</v>
       </c>
@@ -8035,7 +8035,7 @@
       </c>
       <c r="J225" s="7"/>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>148</v>
       </c>
@@ -8063,7 +8063,7 @@
       </c>
       <c r="J226" s="7"/>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>148</v>
       </c>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="J227" s="7"/>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>148</v>
       </c>
@@ -8119,7 +8119,7 @@
       </c>
       <c r="J228" s="7"/>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
         <v>150</v>
       </c>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="J229" s="7"/>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>150</v>
       </c>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="J230" s="7"/>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>152</v>
       </c>
@@ -8205,7 +8205,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
         <v>152</v>
       </c>
@@ -8233,7 +8233,7 @@
       </c>
       <c r="J232" s="7"/>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
         <v>152</v>
       </c>
@@ -8261,7 +8261,7 @@
       </c>
       <c r="J233" s="7"/>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
         <v>152</v>
       </c>
@@ -8289,7 +8289,7 @@
       </c>
       <c r="J234" s="7"/>
     </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
         <v>152</v>
       </c>
@@ -8317,7 +8317,7 @@
       </c>
       <c r="J235" s="7"/>
     </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
         <v>152</v>
       </c>
@@ -8345,7 +8345,7 @@
       </c>
       <c r="J236" s="7"/>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
         <v>152</v>
       </c>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="J237" s="7"/>
     </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
         <v>152</v>
       </c>
@@ -8401,7 +8401,7 @@
       </c>
       <c r="J238" s="7"/>
     </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
         <v>152</v>
       </c>
@@ -8429,7 +8429,7 @@
       </c>
       <c r="J239" s="7"/>
     </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
         <v>152</v>
       </c>
@@ -8457,7 +8457,7 @@
       </c>
       <c r="J240" s="7"/>
     </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>152</v>
       </c>
@@ -8485,7 +8485,7 @@
       </c>
       <c r="J241" s="7"/>
     </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>152</v>
       </c>
@@ -8513,7 +8513,7 @@
       </c>
       <c r="J242" s="7"/>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>154</v>
       </c>
@@ -8541,7 +8541,7 @@
       </c>
       <c r="J243" s="7"/>
     </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>154</v>
       </c>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="J244" s="7"/>
     </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>154</v>
       </c>
@@ -8597,7 +8597,7 @@
       </c>
       <c r="J245" s="7"/>
     </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>154</v>
       </c>
@@ -8625,7 +8625,7 @@
       </c>
       <c r="J246" s="7"/>
     </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>154</v>
       </c>
@@ -8653,7 +8653,7 @@
       </c>
       <c r="J247" s="7"/>
     </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>154</v>
       </c>
@@ -8681,7 +8681,7 @@
       </c>
       <c r="J248" s="7"/>
     </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>154</v>
       </c>
@@ -8709,7 +8709,7 @@
       </c>
       <c r="J249" s="7"/>
     </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>154</v>
       </c>
@@ -8737,7 +8737,7 @@
       </c>
       <c r="J250" s="7"/>
     </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>154</v>
       </c>
@@ -8765,7 +8765,7 @@
       </c>
       <c r="J251" s="7"/>
     </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>154</v>
       </c>
@@ -8793,7 +8793,7 @@
       </c>
       <c r="J252" s="7"/>
     </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>154</v>
       </c>
@@ -8821,7 +8821,7 @@
       </c>
       <c r="J253" s="7"/>
     </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>154</v>
       </c>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="J254" s="7"/>
     </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>156</v>
       </c>
@@ -8877,7 +8877,7 @@
       </c>
       <c r="J255" s="7"/>
     </row>
-    <row r="256" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>156</v>
       </c>
@@ -8905,7 +8905,7 @@
       </c>
       <c r="J256" s="7"/>
     </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>156</v>
       </c>
@@ -8933,7 +8933,7 @@
       </c>
       <c r="J257" s="7"/>
     </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>156</v>
       </c>
@@ -8961,7 +8961,7 @@
       </c>
       <c r="J258" s="7"/>
     </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>156</v>
       </c>
@@ -8989,7 +8989,7 @@
       </c>
       <c r="J259" s="7"/>
     </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>156</v>
       </c>
@@ -9017,7 +9017,7 @@
       </c>
       <c r="J260" s="7"/>
     </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>156</v>
       </c>
@@ -9045,7 +9045,7 @@
       </c>
       <c r="J261" s="7"/>
     </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>156</v>
       </c>
@@ -9073,7 +9073,7 @@
       </c>
       <c r="J262" s="7"/>
     </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>156</v>
       </c>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="J263" s="7"/>
     </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>156</v>
       </c>
@@ -9129,7 +9129,7 @@
       </c>
       <c r="J264" s="7"/>
     </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>156</v>
       </c>
@@ -9157,7 +9157,7 @@
       </c>
       <c r="J265" s="7"/>
     </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>156</v>
       </c>
@@ -9185,7 +9185,7 @@
       </c>
       <c r="J266" s="7"/>
     </row>
-    <row r="267" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>158</v>
       </c>
@@ -9213,7 +9213,7 @@
       </c>
       <c r="J267" s="7"/>
     </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>158</v>
       </c>
@@ -9241,7 +9241,7 @@
       </c>
       <c r="J268" s="7"/>
     </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>158</v>
       </c>
@@ -9269,7 +9269,7 @@
       </c>
       <c r="J269" s="7"/>
     </row>
-    <row r="270" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>158</v>
       </c>
@@ -9297,7 +9297,7 @@
       </c>
       <c r="J270" s="7"/>
     </row>
-    <row r="271" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>158</v>
       </c>
@@ -9325,7 +9325,7 @@
       </c>
       <c r="J271" s="7"/>
     </row>
-    <row r="272" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>158</v>
       </c>
@@ -9353,7 +9353,7 @@
       </c>
       <c r="J272" s="7"/>
     </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>158</v>
       </c>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="J273" s="7"/>
     </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>158</v>
       </c>
@@ -9409,7 +9409,7 @@
       </c>
       <c r="J274" s="7"/>
     </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>158</v>
       </c>
@@ -9437,7 +9437,7 @@
       </c>
       <c r="J275" s="7"/>
     </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
         <v>158</v>
       </c>
@@ -9465,7 +9465,7 @@
       </c>
       <c r="J276" s="7"/>
     </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
         <v>158</v>
       </c>
@@ -9493,7 +9493,7 @@
       </c>
       <c r="J277" s="7"/>
     </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
         <v>158</v>
       </c>
@@ -9521,7 +9521,7 @@
       </c>
       <c r="J278" s="7"/>
     </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
         <v>164</v>
       </c>
@@ -9551,7 +9551,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
         <v>164</v>
       </c>
@@ -9579,7 +9579,7 @@
       </c>
       <c r="J280" s="7"/>
     </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
         <v>164</v>
       </c>
@@ -9607,7 +9607,7 @@
       </c>
       <c r="J281" s="7"/>
     </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
         <v>164</v>
       </c>
@@ -9635,7 +9635,7 @@
       </c>
       <c r="J282" s="7"/>
     </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
         <v>164</v>
       </c>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="J283" s="7"/>
     </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
         <v>164</v>
       </c>
@@ -9691,7 +9691,7 @@
       </c>
       <c r="J284" s="7"/>
     </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
         <v>164</v>
       </c>
@@ -9719,7 +9719,7 @@
       </c>
       <c r="J285" s="7"/>
     </row>
-    <row r="286" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
         <v>164</v>
       </c>
@@ -9747,7 +9747,7 @@
       </c>
       <c r="J286" s="7"/>
     </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
         <v>164</v>
       </c>
@@ -9775,7 +9775,7 @@
       </c>
       <c r="J287" s="7"/>
     </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
         <v>164</v>
       </c>
@@ -9803,7 +9803,7 @@
       </c>
       <c r="J288" s="7"/>
     </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>165</v>
       </c>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="J289" s="7"/>
     </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>165</v>
       </c>
@@ -9859,7 +9859,7 @@
       </c>
       <c r="J290" s="7"/>
     </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>165</v>
       </c>
@@ -9887,7 +9887,7 @@
       </c>
       <c r="J291" s="7"/>
     </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>165</v>
       </c>
@@ -9915,7 +9915,7 @@
       </c>
       <c r="J292" s="7"/>
     </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>165</v>
       </c>
@@ -9943,7 +9943,7 @@
       </c>
       <c r="J293" s="7"/>
     </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>165</v>
       </c>
@@ -9971,7 +9971,7 @@
       </c>
       <c r="J294" s="7"/>
     </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>165</v>
       </c>
@@ -9999,7 +9999,7 @@
       </c>
       <c r="J295" s="7"/>
     </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>165</v>
       </c>
@@ -10027,7 +10027,7 @@
       </c>
       <c r="J296" s="7"/>
     </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>167</v>
       </c>
@@ -10057,7 +10057,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>167</v>
       </c>
@@ -10086,7 +10086,7 @@
       </c>
       <c r="J298" s="7"/>
     </row>
-    <row r="299" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>167</v>
       </c>
@@ -10115,7 +10115,7 @@
       </c>
       <c r="J299" s="7"/>
     </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>167</v>
       </c>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="J300" s="7"/>
     </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>167</v>
       </c>
@@ -10172,7 +10172,7 @@
       </c>
       <c r="J301" s="7"/>
     </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>167</v>
       </c>
@@ -10201,7 +10201,7 @@
       </c>
       <c r="J302" s="7"/>
     </row>
-    <row r="303" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>171</v>
       </c>
@@ -10231,7 +10231,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="304" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>171</v>
       </c>
@@ -10259,7 +10259,7 @@
       </c>
       <c r="J304" s="7"/>
     </row>
-    <row r="305" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>171</v>
       </c>
@@ -10287,7 +10287,7 @@
       </c>
       <c r="J305" s="7"/>
     </row>
-    <row r="306" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>171</v>
       </c>
@@ -10315,7 +10315,7 @@
       </c>
       <c r="J306" s="7"/>
     </row>
-    <row r="307" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>171</v>
       </c>
@@ -10343,7 +10343,7 @@
       </c>
       <c r="J307" s="7"/>
     </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
         <v>171</v>
       </c>
@@ -10371,7 +10371,7 @@
       </c>
       <c r="J308" s="7"/>
     </row>
-    <row r="309" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>171</v>
       </c>
@@ -10399,7 +10399,7 @@
       </c>
       <c r="J309" s="7"/>
     </row>
-    <row r="310" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
         <v>171</v>
       </c>
@@ -10427,7 +10427,7 @@
       </c>
       <c r="J310" s="7"/>
     </row>
-    <row r="311" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>171</v>
       </c>
@@ -10455,7 +10455,7 @@
       </c>
       <c r="J311" s="7"/>
     </row>
-    <row r="312" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>171</v>
       </c>
@@ -10483,7 +10483,7 @@
       </c>
       <c r="J312" s="7"/>
     </row>
-    <row r="313" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>171</v>
       </c>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="J313" s="7"/>
     </row>
-    <row r="314" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>171</v>
       </c>
@@ -10539,7 +10539,7 @@
       </c>
       <c r="J314" s="7"/>
     </row>
-    <row r="315" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
         <v>171</v>
       </c>
@@ -10567,7 +10567,7 @@
       </c>
       <c r="J315" s="7"/>
     </row>
-    <row r="316" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
         <v>171</v>
       </c>
@@ -10595,7 +10595,7 @@
       </c>
       <c r="J316" s="7"/>
     </row>
-    <row r="317" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
         <v>171</v>
       </c>
@@ -10623,7 +10623,7 @@
       </c>
       <c r="J317" s="7"/>
     </row>
-    <row r="318" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>171</v>
       </c>
@@ -10651,7 +10651,7 @@
       </c>
       <c r="J318" s="7"/>
     </row>
-    <row r="319" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>173</v>
       </c>
@@ -10681,7 +10681,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="320" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>173</v>
       </c>
@@ -10709,7 +10709,7 @@
       </c>
       <c r="J320" s="7"/>
     </row>
-    <row r="321" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
         <v>173</v>
       </c>
@@ -10737,7 +10737,7 @@
       </c>
       <c r="J321" s="7"/>
     </row>
-    <row r="322" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
         <v>173</v>
       </c>
@@ -10765,7 +10765,7 @@
       </c>
       <c r="J322" s="7"/>
     </row>
-    <row r="323" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
         <v>176</v>
       </c>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="J323" s="7"/>
     </row>
-    <row r="324" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
         <v>176</v>
       </c>
@@ -10821,7 +10821,7 @@
       </c>
       <c r="J324" s="7"/>
     </row>
-    <row r="325" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
         <v>176</v>
       </c>
@@ -10849,7 +10849,7 @@
       </c>
       <c r="J325" s="7"/>
     </row>
-    <row r="326" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
         <v>176</v>
       </c>
@@ -10877,7 +10877,7 @@
       </c>
       <c r="J326" s="7"/>
     </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
         <v>177</v>
       </c>
@@ -10905,7 +10905,7 @@
       </c>
       <c r="J327" s="7"/>
     </row>
-    <row r="328" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
         <v>177</v>
       </c>
@@ -10933,7 +10933,7 @@
       </c>
       <c r="J328" s="7"/>
     </row>
-    <row r="329" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
         <v>177</v>
       </c>
@@ -10961,7 +10961,7 @@
       </c>
       <c r="J329" s="7"/>
     </row>
-    <row r="330" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
         <v>179</v>
       </c>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="J330" s="7"/>
     </row>
-    <row r="331" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
         <v>179</v>
       </c>
@@ -11017,7 +11017,7 @@
       </c>
       <c r="J331" s="7"/>
     </row>
-    <row r="332" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
         <v>179</v>
       </c>
@@ -11045,7 +11045,7 @@
       </c>
       <c r="J332" s="7"/>
     </row>
-    <row r="333" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
         <v>182</v>
       </c>
@@ -11075,7 +11075,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="334" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
         <v>182</v>
       </c>
@@ -11103,7 +11103,7 @@
       </c>
       <c r="J334" s="7"/>
     </row>
-    <row r="335" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
         <v>184</v>
       </c>
@@ -11131,7 +11131,7 @@
       </c>
       <c r="J335" s="7"/>
     </row>
-    <row r="336" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
         <v>184</v>
       </c>
@@ -11159,7 +11159,7 @@
       </c>
       <c r="J336" s="7"/>
     </row>
-    <row r="337" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
         <v>186</v>
       </c>
@@ -11187,7 +11187,7 @@
       </c>
       <c r="J337" s="7"/>
     </row>
-    <row r="338" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
         <v>186</v>
       </c>
@@ -11215,7 +11215,7 @@
       </c>
       <c r="J338" s="7"/>
     </row>
-    <row r="339" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
         <v>186</v>
       </c>
@@ -11243,7 +11243,7 @@
       </c>
       <c r="J339" s="7"/>
     </row>
-    <row r="340" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
         <v>186</v>
       </c>
@@ -11271,7 +11271,7 @@
       </c>
       <c r="J340" s="7"/>
     </row>
-    <row r="341" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
         <v>188</v>
       </c>
@@ -11299,7 +11299,7 @@
       </c>
       <c r="J341" s="7"/>
     </row>
-    <row r="342" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
         <v>188</v>
       </c>
@@ -11327,7 +11327,7 @@
       </c>
       <c r="J342" s="7"/>
     </row>
-    <row r="343" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
         <v>188</v>
       </c>
@@ -11355,7 +11355,7 @@
       </c>
       <c r="J343" s="7"/>
     </row>
-    <row r="344" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
         <v>188</v>
       </c>
@@ -11383,7 +11383,7 @@
       </c>
       <c r="J344" s="7"/>
     </row>
-    <row r="345" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
         <v>190</v>
       </c>
@@ -11411,7 +11411,7 @@
       </c>
       <c r="J345" s="7"/>
     </row>
-    <row r="346" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
         <v>190</v>
       </c>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="J346" s="7"/>
     </row>
-    <row r="347" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
         <v>190</v>
       </c>
@@ -11467,7 +11467,7 @@
       </c>
       <c r="J347" s="7"/>
     </row>
-    <row r="348" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
         <v>192</v>
       </c>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="J348" s="7"/>
     </row>
-    <row r="349" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
         <v>192</v>
       </c>
@@ -11523,7 +11523,7 @@
       </c>
       <c r="J349" s="7"/>
     </row>
-    <row r="350" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
         <v>192</v>
       </c>
@@ -11551,7 +11551,7 @@
       </c>
       <c r="J350" s="7"/>
     </row>
-    <row r="351" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
         <v>192</v>
       </c>
@@ -11579,7 +11579,7 @@
       </c>
       <c r="J351" s="7"/>
     </row>
-    <row r="352" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
         <v>194</v>
       </c>
@@ -11607,7 +11607,7 @@
       </c>
       <c r="J352" s="7"/>
     </row>
-    <row r="353" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
         <v>194</v>
       </c>
@@ -11635,7 +11635,7 @@
       </c>
       <c r="J353" s="7"/>
     </row>
-    <row r="354" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
         <v>194</v>
       </c>
@@ -11663,7 +11663,7 @@
       </c>
       <c r="J354" s="7"/>
     </row>
-    <row r="355" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
         <v>196</v>
       </c>
@@ -11691,7 +11691,7 @@
       </c>
       <c r="J355" s="7"/>
     </row>
-    <row r="356" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
         <v>196</v>
       </c>
@@ -11719,7 +11719,7 @@
       </c>
       <c r="J356" s="7"/>
     </row>
-    <row r="357" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
         <v>196</v>
       </c>
@@ -11747,7 +11747,7 @@
       </c>
       <c r="J357" s="7"/>
     </row>
-    <row r="358" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
         <v>198</v>
       </c>
@@ -11775,7 +11775,7 @@
       </c>
       <c r="J358" s="7"/>
     </row>
-    <row r="359" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
         <v>198</v>
       </c>
@@ -11803,7 +11803,7 @@
       </c>
       <c r="J359" s="7"/>
     </row>
-    <row r="360" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
         <v>198</v>
       </c>
@@ -11831,7 +11831,7 @@
       </c>
       <c r="J360" s="7"/>
     </row>
-    <row r="361" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
         <v>200</v>
       </c>
@@ -11859,7 +11859,7 @@
       </c>
       <c r="J361" s="7"/>
     </row>
-    <row r="362" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
         <v>200</v>
       </c>
@@ -11887,7 +11887,7 @@
       </c>
       <c r="J362" s="7"/>
     </row>
-    <row r="363" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
         <v>200</v>
       </c>
@@ -11915,7 +11915,7 @@
       </c>
       <c r="J363" s="7"/>
     </row>
-    <row r="364" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
         <v>200</v>
       </c>
@@ -11943,7 +11943,7 @@
       </c>
       <c r="J364" s="7"/>
     </row>
-    <row r="365" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
         <v>203</v>
       </c>
@@ -11971,7 +11971,7 @@
       </c>
       <c r="J365" s="7"/>
     </row>
-    <row r="366" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
         <v>203</v>
       </c>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="J366" s="7"/>
     </row>
-    <row r="367" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
         <v>203</v>
       </c>
@@ -12027,7 +12027,7 @@
       </c>
       <c r="J367" s="7"/>
     </row>
-    <row r="368" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
         <v>206</v>
       </c>
@@ -12057,7 +12057,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="369" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
         <v>206</v>
       </c>
@@ -12085,7 +12085,7 @@
       </c>
       <c r="J369" s="7"/>
     </row>
-    <row r="370" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
         <v>206</v>
       </c>
@@ -12113,7 +12113,7 @@
       </c>
       <c r="J370" s="7"/>
     </row>
-    <row r="371" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
         <v>206</v>
       </c>
@@ -12141,7 +12141,7 @@
       </c>
       <c r="J371" s="7"/>
     </row>
-    <row r="372" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
         <v>208</v>
       </c>
@@ -12169,7 +12169,7 @@
       </c>
       <c r="J372" s="7"/>
     </row>
-    <row r="373" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
         <v>210</v>
       </c>
@@ -12197,7 +12197,7 @@
       </c>
       <c r="J373" s="7"/>
     </row>
-    <row r="374" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
         <v>213</v>
       </c>
@@ -12227,7 +12227,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="375" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
         <v>213</v>
       </c>
@@ -12255,7 +12255,7 @@
       </c>
       <c r="J375" s="7"/>
     </row>
-    <row r="376" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
         <v>213</v>
       </c>
@@ -12283,7 +12283,7 @@
       </c>
       <c r="J376" s="7"/>
     </row>
-    <row r="377" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
         <v>213</v>
       </c>
@@ -12311,7 +12311,7 @@
       </c>
       <c r="J377" s="7"/>
     </row>
-    <row r="378" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
         <v>216</v>
       </c>
@@ -12341,7 +12341,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="379" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
         <v>216</v>
       </c>
@@ -12369,7 +12369,7 @@
       </c>
       <c r="J379" s="7"/>
     </row>
-    <row r="380" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
         <v>216</v>
       </c>
@@ -12397,7 +12397,7 @@
       </c>
       <c r="J380" s="7"/>
     </row>
-    <row r="381" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
         <v>216</v>
       </c>
@@ -12425,7 +12425,7 @@
       </c>
       <c r="J381" s="7"/>
     </row>
-    <row r="382" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
         <v>216</v>
       </c>
@@ -12453,7 +12453,7 @@
       </c>
       <c r="J382" s="7"/>
     </row>
-    <row r="383" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
         <v>216</v>
       </c>
@@ -12481,7 +12481,7 @@
       </c>
       <c r="J383" s="7"/>
     </row>
-    <row r="384" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
         <v>216</v>
       </c>
@@ -12509,7 +12509,7 @@
       </c>
       <c r="J384" s="7"/>
     </row>
-    <row r="385" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
         <v>216</v>
       </c>
@@ -12537,7 +12537,7 @@
       </c>
       <c r="J385" s="7"/>
     </row>
-    <row r="386" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
         <v>216</v>
       </c>
@@ -12565,7 +12565,7 @@
       </c>
       <c r="J386" s="7"/>
     </row>
-    <row r="387" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
         <v>216</v>
       </c>
@@ -12593,7 +12593,7 @@
       </c>
       <c r="J387" s="7"/>
     </row>
-    <row r="388" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
         <v>216</v>
       </c>
@@ -12621,7 +12621,7 @@
       </c>
       <c r="J388" s="7"/>
     </row>
-    <row r="389" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
         <v>216</v>
       </c>
@@ -12649,7 +12649,7 @@
       </c>
       <c r="J389" s="7"/>
     </row>
-    <row r="390" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
         <v>105</v>
       </c>
@@ -12679,7 +12679,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="391" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
         <v>105</v>
       </c>
@@ -12707,7 +12707,7 @@
       </c>
       <c r="J391" s="7"/>
     </row>
-    <row r="392" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
         <v>105</v>
       </c>
@@ -12735,7 +12735,7 @@
       </c>
       <c r="J392" s="7"/>
     </row>
-    <row r="393" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
         <v>105</v>
       </c>
@@ -12763,7 +12763,7 @@
       </c>
       <c r="J393" s="7"/>
     </row>
-    <row r="394" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
         <v>219</v>
       </c>
@@ -12791,7 +12791,7 @@
       </c>
       <c r="J394" s="7"/>
     </row>
-    <row r="395" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
         <v>219</v>
       </c>
@@ -12819,7 +12819,7 @@
       </c>
       <c r="J395" s="7"/>
     </row>
-    <row r="396" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
         <v>219</v>
       </c>
@@ -12847,7 +12847,7 @@
       </c>
       <c r="J396" s="7"/>
     </row>
-    <row r="397" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
         <v>219</v>
       </c>
@@ -12875,7 +12875,7 @@
       </c>
       <c r="J397" s="7"/>
     </row>
-    <row r="398" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
         <v>97</v>
       </c>
@@ -12903,7 +12903,7 @@
       </c>
       <c r="J398" s="7"/>
     </row>
-    <row r="399" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
         <v>97</v>
       </c>
@@ -12931,7 +12931,7 @@
       </c>
       <c r="J399" s="7"/>
     </row>
-    <row r="400" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
         <v>97</v>
       </c>
@@ -12959,7 +12959,7 @@
       </c>
       <c r="J400" s="7"/>
     </row>
-    <row r="401" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
         <v>97</v>
       </c>
@@ -12987,7 +12987,7 @@
       </c>
       <c r="J401" s="7"/>
     </row>
-    <row r="402" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
         <v>99</v>
       </c>
@@ -13015,7 +13015,7 @@
       </c>
       <c r="J402" s="7"/>
     </row>
-    <row r="403" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
         <v>99</v>
       </c>
@@ -13043,7 +13043,7 @@
       </c>
       <c r="J403" s="7"/>
     </row>
-    <row r="404" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
         <v>99</v>
       </c>
@@ -13071,7 +13071,7 @@
       </c>
       <c r="J404" s="7"/>
     </row>
-    <row r="405" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
         <v>99</v>
       </c>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="J405" s="7"/>
     </row>
-    <row r="406" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
         <v>221</v>
       </c>
@@ -13127,7 +13127,7 @@
       </c>
       <c r="J406" s="7"/>
     </row>
-    <row r="407" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
         <v>221</v>
       </c>
@@ -13155,7 +13155,7 @@
       </c>
       <c r="J407" s="7"/>
     </row>
-    <row r="408" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
         <v>221</v>
       </c>
@@ -13183,7 +13183,7 @@
       </c>
       <c r="J408" s="7"/>
     </row>
-    <row r="409" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
         <v>221</v>
       </c>
@@ -13211,7 +13211,7 @@
       </c>
       <c r="J409" s="7"/>
     </row>
-    <row r="410" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
         <v>222</v>
       </c>
@@ -13239,7 +13239,7 @@
       </c>
       <c r="J410" s="7"/>
     </row>
-    <row r="411" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
         <v>222</v>
       </c>
@@ -13267,7 +13267,7 @@
       </c>
       <c r="J411" s="7"/>
     </row>
-    <row r="412" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
         <v>222</v>
       </c>
@@ -13295,7 +13295,7 @@
       </c>
       <c r="J412" s="7"/>
     </row>
-    <row r="413" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
         <v>222</v>
       </c>
@@ -13323,7 +13323,7 @@
       </c>
       <c r="J413" s="7"/>
     </row>
-    <row r="414" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
         <v>223</v>
       </c>
@@ -13351,7 +13351,7 @@
       </c>
       <c r="J414" s="7"/>
     </row>
-    <row r="415" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
         <v>223</v>
       </c>
@@ -13379,7 +13379,7 @@
       </c>
       <c r="J415" s="7"/>
     </row>
-    <row r="416" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
         <v>223</v>
       </c>
@@ -13407,7 +13407,7 @@
       </c>
       <c r="J416" s="7"/>
     </row>
-    <row r="417" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
         <v>223</v>
       </c>
@@ -13435,7 +13435,7 @@
       </c>
       <c r="J417" s="7"/>
     </row>
-    <row r="418" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
         <v>225</v>
       </c>
@@ -13463,7 +13463,7 @@
       </c>
       <c r="J418" s="7"/>
     </row>
-    <row r="419" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
         <v>225</v>
       </c>
@@ -13491,7 +13491,7 @@
       </c>
       <c r="J419" s="7"/>
     </row>
-    <row r="420" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
         <v>225</v>
       </c>
@@ -13519,7 +13519,7 @@
       </c>
       <c r="J420" s="7"/>
     </row>
-    <row r="421" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
         <v>225</v>
       </c>
@@ -13547,7 +13547,7 @@
       </c>
       <c r="J421" s="7"/>
     </row>
-    <row r="422" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
         <v>227</v>
       </c>
@@ -13575,7 +13575,7 @@
       </c>
       <c r="J422" s="7"/>
     </row>
-    <row r="423" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
         <v>227</v>
       </c>
@@ -13603,7 +13603,7 @@
       </c>
       <c r="J423" s="7"/>
     </row>
-    <row r="424" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
         <v>227</v>
       </c>
@@ -13631,7 +13631,7 @@
       </c>
       <c r="J424" s="7"/>
     </row>
-    <row r="425" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
         <v>227</v>
       </c>
@@ -13659,7 +13659,7 @@
       </c>
       <c r="J425" s="7"/>
     </row>
-    <row r="426" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
         <v>229</v>
       </c>
@@ -13687,7 +13687,7 @@
       </c>
       <c r="J426" s="7"/>
     </row>
-    <row r="427" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
         <v>229</v>
       </c>
@@ -13715,7 +13715,7 @@
       </c>
       <c r="J427" s="7"/>
     </row>
-    <row r="428" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
         <v>229</v>
       </c>
@@ -13743,7 +13743,7 @@
       </c>
       <c r="J428" s="7"/>
     </row>
-    <row r="429" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
         <v>229</v>
       </c>
@@ -13771,7 +13771,7 @@
       </c>
       <c r="J429" s="7"/>
     </row>
-    <row r="430" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
         <v>234</v>
       </c>
@@ -13801,7 +13801,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="431" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
         <v>240</v>
       </c>
@@ -13829,7 +13829,7 @@
       </c>
       <c r="J431" s="7"/>
     </row>
-    <row r="432" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
         <v>241</v>
       </c>
@@ -13857,7 +13857,7 @@
       </c>
       <c r="J432" s="7"/>
     </row>
-    <row r="433" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
         <v>239</v>
       </c>
@@ -13885,7 +13885,7 @@
       </c>
       <c r="J433" s="7"/>
     </row>
-    <row r="434" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
         <v>239</v>
       </c>
@@ -13913,7 +13913,7 @@
       </c>
       <c r="J434" s="7"/>
     </row>
-    <row r="435" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
         <v>244</v>
       </c>
@@ -13941,7 +13941,7 @@
       </c>
       <c r="J435" s="7"/>
     </row>
-    <row r="436" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
         <v>244</v>
       </c>
@@ -13969,7 +13969,7 @@
       </c>
       <c r="J436" s="7"/>
     </row>
-    <row r="437" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
         <v>248</v>
       </c>
@@ -13999,7 +13999,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="438" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
         <v>240</v>
       </c>
@@ -14027,7 +14027,7 @@
       </c>
       <c r="J438" s="7"/>
     </row>
-    <row r="439" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
         <v>241</v>
       </c>
@@ -14055,7 +14055,7 @@
       </c>
       <c r="J439" s="7"/>
     </row>
-    <row r="440" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
         <v>248</v>
       </c>
@@ -14083,7 +14083,7 @@
       </c>
       <c r="J440" s="7"/>
     </row>
-    <row r="441" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
         <v>240</v>
       </c>
@@ -14111,7 +14111,7 @@
       </c>
       <c r="J441" s="7"/>
     </row>
-    <row r="442" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
         <v>241</v>
       </c>
@@ -14139,7 +14139,7 @@
       </c>
       <c r="J442" s="7"/>
     </row>
-    <row r="443" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:10" ht="58" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
         <v>249</v>
       </c>
@@ -14169,7 +14169,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="444" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
         <v>117</v>
       </c>
@@ -14199,7 +14199,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="445" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
         <v>117</v>
       </c>
@@ -14227,7 +14227,7 @@
       </c>
       <c r="J445" s="7"/>
     </row>
-    <row r="446" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
         <v>117</v>
       </c>
@@ -14255,7 +14255,7 @@
       </c>
       <c r="J446" s="7"/>
     </row>
-    <row r="447" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
         <v>117</v>
       </c>
@@ -14283,7 +14283,7 @@
       </c>
       <c r="J447" s="7"/>
     </row>
-    <row r="448" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
         <v>213</v>
       </c>
@@ -14313,7 +14313,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="449" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
         <v>213</v>
       </c>
@@ -14341,7 +14341,7 @@
       </c>
       <c r="J449" s="7"/>
     </row>
-    <row r="450" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
         <v>213</v>
       </c>
@@ -14369,7 +14369,7 @@
       </c>
       <c r="J450" s="7"/>
     </row>
-    <row r="451" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
         <v>213</v>
       </c>
@@ -14397,7 +14397,7 @@
       </c>
       <c r="J451" s="7"/>
     </row>
-    <row r="452" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
         <v>254</v>
       </c>
@@ -14425,7 +14425,7 @@
       </c>
       <c r="J452" s="7"/>
     </row>
-    <row r="453" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
         <v>254</v>
       </c>
@@ -14453,7 +14453,7 @@
       </c>
       <c r="J453" s="7"/>
     </row>
-    <row r="454" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
         <v>254</v>
       </c>
@@ -14481,7 +14481,7 @@
       </c>
       <c r="J454" s="7"/>
     </row>
-    <row r="455" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
         <v>254</v>
       </c>
@@ -14509,7 +14509,7 @@
       </c>
       <c r="J455" s="7"/>
     </row>
-    <row r="456" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
         <v>255</v>
       </c>
@@ -14537,7 +14537,7 @@
       </c>
       <c r="J456" s="7"/>
     </row>
-    <row r="457" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
         <v>255</v>
       </c>
@@ -14565,7 +14565,7 @@
       </c>
       <c r="J457" s="7"/>
     </row>
-    <row r="458" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
         <v>255</v>
       </c>
@@ -14593,7 +14593,7 @@
       </c>
       <c r="J458" s="7"/>
     </row>
-    <row r="459" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
         <v>255</v>
       </c>
@@ -14621,12 +14621,12 @@
       </c>
       <c r="J459" s="7"/>
     </row>
-    <row r="460" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
         <v>259</v>
       </c>
       <c r="B460" t="s">
-        <v>260</v>
+        <v>304</v>
       </c>
       <c r="C460">
         <v>83.015873015872998</v>
@@ -14648,15 +14648,15 @@
         <v>0.74584182366527296</v>
       </c>
       <c r="J460" s="7" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="461" spans="1:10" x14ac:dyDescent="0.25">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="461" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
         <v>259</v>
       </c>
       <c r="B461" t="s">
-        <v>260</v>
+        <v>304</v>
       </c>
       <c r="C461">
         <v>111.98412698412599</v>
@@ -14679,12 +14679,12 @@
       </c>
       <c r="J461" s="7"/>
     </row>
-    <row r="462" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
         <v>259</v>
       </c>
       <c r="B462" t="s">
-        <v>260</v>
+        <v>304</v>
       </c>
       <c r="C462">
         <v>134.60317460317401</v>
@@ -14707,12 +14707,12 @@
       </c>
       <c r="J462" s="7"/>
     </row>
-    <row r="463" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
         <v>259</v>
       </c>
       <c r="B463" t="s">
-        <v>260</v>
+        <v>304</v>
       </c>
       <c r="C463">
         <v>153.65079365079299</v>
@@ -14735,12 +14735,12 @@
       </c>
       <c r="J463" s="7"/>
     </row>
-    <row r="464" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
         <v>259</v>
       </c>
       <c r="B464" t="s">
-        <v>260</v>
+        <v>304</v>
       </c>
       <c r="C464">
         <v>169.12698412698401</v>
@@ -14763,12 +14763,12 @@
       </c>
       <c r="J464" s="7"/>
     </row>
-    <row r="465" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
+        <v>260</v>
+      </c>
+      <c r="B465" t="s">
         <v>261</v>
-      </c>
-      <c r="B465" t="s">
-        <v>262</v>
       </c>
       <c r="C465">
         <v>82.2222222222222</v>
@@ -14791,12 +14791,12 @@
       </c>
       <c r="J465" s="7"/>
     </row>
-    <row r="466" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
+        <v>260</v>
+      </c>
+      <c r="B466" t="s">
         <v>261</v>
-      </c>
-      <c r="B466" t="s">
-        <v>262</v>
       </c>
       <c r="C466">
         <v>112.380952380952</v>
@@ -14819,12 +14819,12 @@
       </c>
       <c r="J466" s="7"/>
     </row>
-    <row r="467" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
+        <v>260</v>
+      </c>
+      <c r="B467" t="s">
         <v>261</v>
-      </c>
-      <c r="B467" t="s">
-        <v>262</v>
       </c>
       <c r="C467">
         <v>134.20634920634899</v>
@@ -14847,12 +14847,12 @@
       </c>
       <c r="J467" s="7"/>
     </row>
-    <row r="468" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
+        <v>260</v>
+      </c>
+      <c r="B468" t="s">
         <v>261</v>
-      </c>
-      <c r="B468" t="s">
-        <v>262</v>
       </c>
       <c r="C468">
         <v>154.04761904761901</v>
@@ -14875,12 +14875,12 @@
       </c>
       <c r="J468" s="7"/>
     </row>
-    <row r="469" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
+        <v>260</v>
+      </c>
+      <c r="B469" t="s">
         <v>261</v>
-      </c>
-      <c r="B469" t="s">
-        <v>262</v>
       </c>
       <c r="C469">
         <v>182.619047619047</v>
@@ -14903,12 +14903,12 @@
       </c>
       <c r="J469" s="7"/>
     </row>
-    <row r="470" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
+        <v>262</v>
+      </c>
+      <c r="B470" t="s">
         <v>263</v>
-      </c>
-      <c r="B470" t="s">
-        <v>264</v>
       </c>
       <c r="C470">
         <v>41.349206349206298</v>
@@ -14931,12 +14931,12 @@
       </c>
       <c r="J470" s="7"/>
     </row>
-    <row r="471" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
+        <v>262</v>
+      </c>
+      <c r="B471" t="s">
         <v>263</v>
-      </c>
-      <c r="B471" t="s">
-        <v>264</v>
       </c>
       <c r="C471">
         <v>82.619047619047606</v>
@@ -14959,12 +14959,12 @@
       </c>
       <c r="J471" s="7"/>
     </row>
-    <row r="472" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
+        <v>262</v>
+      </c>
+      <c r="B472" t="s">
         <v>263</v>
-      </c>
-      <c r="B472" t="s">
-        <v>264</v>
       </c>
       <c r="C472">
         <v>134.60317460317401</v>
@@ -14987,12 +14987,12 @@
       </c>
       <c r="J472" s="7"/>
     </row>
-    <row r="473" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
+        <v>262</v>
+      </c>
+      <c r="B473" t="s">
         <v>263</v>
-      </c>
-      <c r="B473" t="s">
-        <v>264</v>
       </c>
       <c r="C473">
         <v>153.253968253968</v>
@@ -15015,12 +15015,12 @@
       </c>
       <c r="J473" s="7"/>
     </row>
-    <row r="474" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
+        <v>262</v>
+      </c>
+      <c r="B474" t="s">
         <v>263</v>
-      </c>
-      <c r="B474" t="s">
-        <v>264</v>
       </c>
       <c r="C474">
         <v>181.82539682539601</v>
@@ -15043,12 +15043,12 @@
       </c>
       <c r="J474" s="7"/>
     </row>
-    <row r="475" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
+        <v>264</v>
+      </c>
+      <c r="B475" t="s">
         <v>265</v>
-      </c>
-      <c r="B475" t="s">
-        <v>266</v>
       </c>
       <c r="C475">
         <v>41.349206349206298</v>
@@ -15071,12 +15071,12 @@
       </c>
       <c r="J475" s="7"/>
     </row>
-    <row r="476" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
+        <v>264</v>
+      </c>
+      <c r="B476" t="s">
         <v>265</v>
-      </c>
-      <c r="B476" t="s">
-        <v>266</v>
       </c>
       <c r="C476">
         <v>81.825396825396794</v>
@@ -15099,12 +15099,12 @@
       </c>
       <c r="J476" s="7"/>
     </row>
-    <row r="477" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
+        <v>264</v>
+      </c>
+      <c r="B477" t="s">
         <v>265</v>
-      </c>
-      <c r="B477" t="s">
-        <v>266</v>
       </c>
       <c r="C477">
         <v>112.777777777777</v>
@@ -15127,12 +15127,12 @@
       </c>
       <c r="J477" s="7"/>
     </row>
-    <row r="478" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
+        <v>264</v>
+      </c>
+      <c r="B478" t="s">
         <v>265</v>
-      </c>
-      <c r="B478" t="s">
-        <v>266</v>
       </c>
       <c r="C478">
         <v>153.65079365079299</v>
@@ -15155,12 +15155,12 @@
       </c>
       <c r="J478" s="7"/>
     </row>
-    <row r="479" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
+        <v>264</v>
+      </c>
+      <c r="B479" t="s">
         <v>265</v>
-      </c>
-      <c r="B479" t="s">
-        <v>266</v>
       </c>
       <c r="C479">
         <v>183.809523809523</v>
@@ -15183,9 +15183,9 @@
       </c>
       <c r="J479" s="7"/>
     </row>
-    <row r="480" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B480" t="s">
         <v>220</v>
@@ -15211,9 +15211,9 @@
       </c>
       <c r="J480" s="7"/>
     </row>
-    <row r="481" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B481" t="s">
         <v>220</v>
@@ -15239,9 +15239,9 @@
       </c>
       <c r="J481" s="7"/>
     </row>
-    <row r="482" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B482" t="s">
         <v>220</v>
@@ -15267,9 +15267,9 @@
       </c>
       <c r="J482" s="7"/>
     </row>
-    <row r="483" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B483" t="s">
         <v>220</v>
@@ -15295,12 +15295,12 @@
       </c>
       <c r="J483" s="7"/>
     </row>
-    <row r="484" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B484" t="s">
-        <v>269</v>
+        <v>305</v>
       </c>
       <c r="C484">
         <v>83.412698412698404</v>
@@ -15323,12 +15323,12 @@
       </c>
       <c r="J484" s="7"/>
     </row>
-    <row r="485" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B485" t="s">
-        <v>269</v>
+        <v>305</v>
       </c>
       <c r="C485">
         <v>111.587301587301</v>
@@ -15351,12 +15351,12 @@
       </c>
       <c r="J485" s="7"/>
     </row>
-    <row r="486" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B486" t="s">
-        <v>269</v>
+        <v>305</v>
       </c>
       <c r="C486">
         <v>135</v>
@@ -15379,12 +15379,12 @@
       </c>
       <c r="J486" s="7"/>
     </row>
-    <row r="487" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B487" t="s">
-        <v>269</v>
+        <v>305</v>
       </c>
       <c r="C487">
         <v>153.65079365079299</v>
@@ -15407,12 +15407,12 @@
       </c>
       <c r="J487" s="7"/>
     </row>
-    <row r="488" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B488" t="s">
-        <v>269</v>
+        <v>305</v>
       </c>
       <c r="C488">
         <v>181.82539682539601</v>
@@ -15435,12 +15435,12 @@
       </c>
       <c r="J488" s="7"/>
     </row>
-    <row r="489" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B489" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C489">
         <v>100</v>
@@ -15462,15 +15462,15 @@
         <v>1.1630826116569999</v>
       </c>
       <c r="J489" s="7" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="490" spans="1:10" x14ac:dyDescent="0.25">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="490" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B490" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C490">
         <v>100</v>
@@ -15493,12 +15493,12 @@
       </c>
       <c r="J490" s="7"/>
     </row>
-    <row r="491" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B491" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C491">
         <v>100</v>
@@ -15521,12 +15521,12 @@
       </c>
       <c r="J491" s="7"/>
     </row>
-    <row r="492" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B492" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C492">
         <v>100</v>
@@ -15549,12 +15549,12 @@
       </c>
       <c r="J492" s="7"/>
     </row>
-    <row r="493" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B493" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C493">
         <v>100</v>
@@ -15577,12 +15577,12 @@
       </c>
       <c r="J493" s="7"/>
     </row>
-    <row r="494" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B494" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C494">
         <v>55</v>
@@ -15605,12 +15605,12 @@
       </c>
       <c r="J494" s="7"/>
     </row>
-    <row r="495" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B495" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C495">
         <v>55</v>
@@ -15633,12 +15633,12 @@
       </c>
       <c r="J495" s="7"/>
     </row>
-    <row r="496" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B496" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C496">
         <v>55</v>
@@ -15661,12 +15661,12 @@
       </c>
       <c r="J496" s="7"/>
     </row>
-    <row r="497" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B497" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C497">
         <v>55</v>
@@ -15689,12 +15689,12 @@
       </c>
       <c r="J497" s="7"/>
     </row>
-    <row r="498" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B498" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C498">
         <v>55</v>
@@ -15717,12 +15717,12 @@
       </c>
       <c r="J498" s="7"/>
     </row>
-    <row r="499" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B499" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C499">
         <v>250</v>
@@ -15744,15 +15744,15 @@
         <v>2.7169652855542998</v>
       </c>
       <c r="J499" s="7" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="500" spans="1:10" x14ac:dyDescent="0.25">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="500" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B500" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C500">
         <v>250</v>
@@ -15775,12 +15775,12 @@
       </c>
       <c r="J500" s="7"/>
     </row>
-    <row r="501" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B501" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C501">
         <v>250</v>
@@ -15803,12 +15803,12 @@
       </c>
       <c r="J501" s="7"/>
     </row>
-    <row r="502" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B502" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C502">
         <v>250</v>
@@ -15831,12 +15831,12 @@
       </c>
       <c r="J502" s="7"/>
     </row>
-    <row r="503" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B503" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C503">
         <v>250</v>
@@ -15859,12 +15859,12 @@
       </c>
       <c r="J503" s="7"/>
     </row>
-    <row r="504" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B504" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C504">
         <v>250</v>
@@ -15887,12 +15887,12 @@
       </c>
       <c r="J504" s="7"/>
     </row>
-    <row r="505" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B505" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C505">
         <v>250</v>
@@ -15915,12 +15915,12 @@
       </c>
       <c r="J505" s="7"/>
     </row>
-    <row r="506" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B506" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C506">
         <v>250</v>
@@ -15943,12 +15943,12 @@
       </c>
       <c r="J506" s="7"/>
     </row>
-    <row r="507" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B507" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C507">
         <v>99.430199430199394</v>
@@ -15972,12 +15972,12 @@
       </c>
       <c r="J507" s="7"/>
     </row>
-    <row r="508" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B508" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C508">
         <v>150.52706552706499</v>
@@ -16001,12 +16001,12 @@
       </c>
       <c r="J508" s="7"/>
     </row>
-    <row r="509" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B509" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C509">
         <v>198.86039886039799</v>
@@ -16030,12 +16030,12 @@
       </c>
       <c r="J509" s="7"/>
     </row>
-    <row r="510" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B510" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C510">
         <v>250.42735042735001</v>
@@ -16059,7 +16059,7 @@
       </c>
       <c r="J510" s="7"/>
     </row>
-    <row r="511" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
         <v>69</v>
       </c>
@@ -16087,7 +16087,7 @@
       </c>
       <c r="J511" s="7"/>
     </row>
-    <row r="512" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
         <v>69</v>
       </c>
@@ -16115,7 +16115,7 @@
       </c>
       <c r="J512" s="7"/>
     </row>
-    <row r="513" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
         <v>69</v>
       </c>
@@ -16143,7 +16143,7 @@
       </c>
       <c r="J513" s="7"/>
     </row>
-    <row r="514" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
         <v>69</v>
       </c>
@@ -16171,7 +16171,7 @@
       </c>
       <c r="J514" s="7"/>
     </row>
-    <row r="515" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
         <v>71</v>
       </c>
@@ -16199,7 +16199,7 @@
       </c>
       <c r="J515" s="7"/>
     </row>
-    <row r="516" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
         <v>71</v>
       </c>
@@ -16227,7 +16227,7 @@
       </c>
       <c r="J516" s="7"/>
     </row>
-    <row r="517" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
         <v>71</v>
       </c>
@@ -16255,7 +16255,7 @@
       </c>
       <c r="J517" s="7"/>
     </row>
-    <row r="518" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
         <v>71</v>
       </c>
@@ -16283,7 +16283,7 @@
       </c>
       <c r="J518" s="7"/>
     </row>
-    <row r="519" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
         <v>73</v>
       </c>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="J519" s="7"/>
     </row>
-    <row r="520" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
         <v>73</v>
       </c>
@@ -16339,7 +16339,7 @@
       </c>
       <c r="J520" s="7"/>
     </row>
-    <row r="521" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
         <v>73</v>
       </c>
@@ -16367,7 +16367,7 @@
       </c>
       <c r="J521" s="7"/>
     </row>
-    <row r="522" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
         <v>73</v>
       </c>
@@ -16395,7 +16395,7 @@
       </c>
       <c r="J522" s="7"/>
     </row>
-    <row r="523" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
         <v>69</v>
       </c>
@@ -16423,7 +16423,7 @@
       </c>
       <c r="J523" s="7"/>
     </row>
-    <row r="524" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
         <v>69</v>
       </c>
@@ -16451,7 +16451,7 @@
       </c>
       <c r="J524" s="7"/>
     </row>
-    <row r="525" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
         <v>69</v>
       </c>
@@ -16479,7 +16479,7 @@
       </c>
       <c r="J525" s="7"/>
     </row>
-    <row r="526" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
         <v>71</v>
       </c>
@@ -16507,7 +16507,7 @@
       </c>
       <c r="J526" s="7"/>
     </row>
-    <row r="527" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
         <v>71</v>
       </c>
@@ -16535,7 +16535,7 @@
       </c>
       <c r="J527" s="7"/>
     </row>
-    <row r="528" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
         <v>71</v>
       </c>
@@ -16563,7 +16563,7 @@
       </c>
       <c r="J528" s="7"/>
     </row>
-    <row r="529" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
         <v>71</v>
       </c>
@@ -16591,7 +16591,7 @@
       </c>
       <c r="J529" s="7"/>
     </row>
-    <row r="530" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
         <v>73</v>
       </c>
@@ -16619,7 +16619,7 @@
       </c>
       <c r="J530" s="7"/>
     </row>
-    <row r="531" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
         <v>73</v>
       </c>
@@ -16647,7 +16647,7 @@
       </c>
       <c r="J531" s="7"/>
     </row>
-    <row r="532" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
         <v>73</v>
       </c>
@@ -16675,9 +16675,9 @@
       </c>
       <c r="J532" s="7"/>
     </row>
-    <row r="533" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B533" t="s">
         <v>236</v>
@@ -16703,12 +16703,12 @@
         <v>1.8355423310855601</v>
       </c>
       <c r="J533" s="7" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="534" spans="1:10" x14ac:dyDescent="0.25">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="534" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B534" t="s">
         <v>237</v>
@@ -16735,9 +16735,9 @@
       </c>
       <c r="J534" s="7"/>
     </row>
-    <row r="535" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B535" t="s">
         <v>238</v>
@@ -16764,9 +16764,9 @@
       </c>
       <c r="J535" s="7"/>
     </row>
-    <row r="536" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B536" t="s">
         <v>236</v>
@@ -16793,9 +16793,9 @@
       </c>
       <c r="J536" s="7"/>
     </row>
-    <row r="537" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B537" t="s">
         <v>237</v>
@@ -16822,9 +16822,9 @@
       </c>
       <c r="J537" s="7"/>
     </row>
-    <row r="538" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B538" t="s">
         <v>238</v>
@@ -16851,9 +16851,9 @@
       </c>
       <c r="J538" s="7"/>
     </row>
-    <row r="539" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B539" t="s">
         <v>236</v>
@@ -16880,9 +16880,9 @@
       </c>
       <c r="J539" s="7"/>
     </row>
-    <row r="540" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B540" t="s">
         <v>237</v>
@@ -16909,9 +16909,9 @@
       </c>
       <c r="J540" s="7"/>
     </row>
-    <row r="541" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B541" t="s">
         <v>238</v>
@@ -16938,9 +16938,9 @@
       </c>
       <c r="J541" s="7"/>
     </row>
-    <row r="542" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B542" t="s">
         <v>236</v>
@@ -16967,9 +16967,9 @@
       </c>
       <c r="J542" s="7"/>
     </row>
-    <row r="543" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B543" t="s">
         <v>237</v>
@@ -16996,9 +16996,9 @@
       </c>
       <c r="J543" s="7"/>
     </row>
-    <row r="544" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B544" t="s">
         <v>238</v>
@@ -17025,9 +17025,9 @@
       </c>
       <c r="J544" s="7"/>
     </row>
-    <row r="545" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B545" t="s">
         <v>236</v>
@@ -17053,9 +17053,9 @@
       </c>
       <c r="J545" s="7"/>
     </row>
-    <row r="546" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B546" t="s">
         <v>237</v>
@@ -17081,9 +17081,9 @@
       </c>
       <c r="J546" s="7"/>
     </row>
-    <row r="547" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B547" t="s">
         <v>238</v>
@@ -17109,9 +17109,9 @@
       </c>
       <c r="J547" s="7"/>
     </row>
-    <row r="548" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B548" t="s">
         <v>237</v>
@@ -17138,9 +17138,9 @@
       </c>
       <c r="J548" s="7"/>
     </row>
-    <row r="549" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B549" t="s">
         <v>238</v>
@@ -17167,9 +17167,9 @@
       </c>
       <c r="J549" s="7"/>
     </row>
-    <row r="550" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B550" t="s">
         <v>237</v>
@@ -17196,9 +17196,9 @@
       </c>
       <c r="J550" s="7"/>
     </row>
-    <row r="551" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B551" t="s">
         <v>238</v>
@@ -17225,12 +17225,12 @@
       </c>
       <c r="J551" s="7"/>
     </row>
-    <row r="552" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B552" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C552">
         <v>100</v>
@@ -17253,15 +17253,15 @@
         <v>13</v>
       </c>
       <c r="J552" s="7" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="553" spans="1:10" x14ac:dyDescent="0.25">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="553" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B553" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C553">
         <v>100</v>
@@ -17285,12 +17285,12 @@
       </c>
       <c r="J553" s="7"/>
     </row>
-    <row r="554" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B554" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C554">
         <v>100</v>
@@ -17314,12 +17314,12 @@
       </c>
       <c r="J554" s="7"/>
     </row>
-    <row r="555" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B555" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C555">
         <v>100</v>
@@ -17343,12 +17343,12 @@
       </c>
       <c r="J555" s="7"/>
     </row>
-    <row r="556" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B556" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C556">
         <v>100</v>
@@ -17372,12 +17372,12 @@
       </c>
       <c r="J556" s="7"/>
     </row>
-    <row r="557" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B557" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C557">
         <v>100</v>
@@ -17400,12 +17400,12 @@
       </c>
       <c r="J557" s="7"/>
     </row>
-    <row r="558" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B558" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C558">
         <v>100</v>
@@ -17429,12 +17429,12 @@
       </c>
       <c r="J558" s="7"/>
     </row>
-    <row r="559" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B559" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C559">
         <v>100</v>
@@ -17458,12 +17458,12 @@
       </c>
       <c r="J559" s="7"/>
     </row>
-    <row r="560" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B560" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C560">
         <v>100</v>
@@ -17486,12 +17486,12 @@
       </c>
       <c r="J560" s="7"/>
     </row>
-    <row r="561" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B561" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C561">
         <v>100</v>
@@ -17514,12 +17514,12 @@
       </c>
       <c r="J561" s="7"/>
     </row>
-    <row r="562" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B562" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C562">
         <v>100</v>
@@ -17542,12 +17542,12 @@
       </c>
       <c r="J562" s="7"/>
     </row>
-    <row r="563" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B563" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C563">
         <v>100</v>
@@ -17570,12 +17570,12 @@
       </c>
       <c r="J563" s="7"/>
     </row>
-    <row r="564" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B564" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C564">
         <v>4</v>
@@ -17597,15 +17597,15 @@
         <v>8.7100000000000009</v>
       </c>
       <c r="J564" s="7" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="565" spans="1:10" x14ac:dyDescent="0.25">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="565" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B565" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C565">
         <v>10</v>
@@ -17628,12 +17628,12 @@
       </c>
       <c r="J565" s="8"/>
     </row>
-    <row r="566" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B566" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C566">
         <v>4</v>
@@ -17656,12 +17656,12 @@
       </c>
       <c r="J566" s="8"/>
     </row>
-    <row r="567" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B567" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C567">
         <v>10</v>
@@ -17684,12 +17684,12 @@
       </c>
       <c r="J567" s="8"/>
     </row>
-    <row r="568" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B568" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C568">
         <v>4</v>
@@ -17712,12 +17712,12 @@
       </c>
       <c r="J568" s="8"/>
     </row>
-    <row r="569" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B569" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C569">
         <v>10</v>
@@ -17740,12 +17740,12 @@
       </c>
       <c r="J569" s="8"/>
     </row>
-    <row r="570" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B570" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C570">
         <v>4</v>
@@ -17768,12 +17768,12 @@
       </c>
       <c r="J570" s="8"/>
     </row>
-    <row r="571" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B571" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C571">
         <v>10</v>
@@ -17796,9 +17796,9 @@
       </c>
       <c r="J571" s="8"/>
     </row>
-    <row r="572" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B572" t="s">
         <v>220</v>
@@ -17824,9 +17824,9 @@
       </c>
       <c r="J572" s="8"/>
     </row>
-    <row r="573" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B573" t="s">
         <v>220</v>
@@ -17851,12 +17851,12 @@
         <v>2.75</v>
       </c>
       <c r="J573" s="7" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="574" spans="1:10" x14ac:dyDescent="0.25">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="574" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B574" t="s">
         <v>220</v>
@@ -17882,9 +17882,9 @@
       </c>
       <c r="J574" s="8"/>
     </row>
-    <row r="575" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B575" t="s">
         <v>220</v>
@@ -17910,9 +17910,9 @@
       </c>
       <c r="J575" s="8"/>
     </row>
-    <row r="576" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B576" t="s">
         <v>220</v>
@@ -17938,9 +17938,9 @@
       </c>
       <c r="J576" s="8"/>
     </row>
-    <row r="577" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B577" t="s">
         <v>220</v>
@@ -17966,12 +17966,12 @@
       </c>
       <c r="J577" s="8"/>
     </row>
-    <row r="578" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B578" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C578">
         <v>60</v>
@@ -17993,15 +17993,15 @@
         <v>5.0159057620259704</v>
       </c>
       <c r="J578" s="7" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="579" spans="1:10" x14ac:dyDescent="0.25">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="579" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B579" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C579">
         <v>60</v>
@@ -18024,12 +18024,12 @@
       </c>
       <c r="J579" s="7"/>
     </row>
-    <row r="580" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B580" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C580">
         <v>60</v>
@@ -18052,12 +18052,12 @@
       </c>
       <c r="J580" s="7"/>
     </row>
-    <row r="581" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B581" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C581">
         <v>60</v>
@@ -18080,12 +18080,12 @@
       </c>
       <c r="J581" s="7"/>
     </row>
-    <row r="582" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B582" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C582">
         <v>60</v>
@@ -18108,12 +18108,12 @@
       </c>
       <c r="J582" s="7"/>
     </row>
-    <row r="583" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B583" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C583">
         <f>100-D583</f>
@@ -18136,15 +18136,15 @@
         <v>2.7825594022071201</v>
       </c>
       <c r="J583" s="7" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="584" spans="1:10" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="584" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B584" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C584">
         <f t="shared" ref="C584:C587" si="48">100-D584</f>
@@ -18168,12 +18168,12 @@
       </c>
       <c r="J584" s="7"/>
     </row>
-    <row r="585" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B585" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C585">
         <f t="shared" si="48"/>
@@ -18197,12 +18197,12 @@
       </c>
       <c r="J585" s="7"/>
     </row>
-    <row r="586" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B586" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C586">
         <f t="shared" si="48"/>
@@ -18226,12 +18226,12 @@
       </c>
       <c r="J586" s="7"/>
     </row>
-    <row r="587" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B587" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C587">
         <f t="shared" si="48"/>
@@ -18255,12 +18255,12 @@
       </c>
       <c r="J587" s="7"/>
     </row>
-    <row r="588" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B588" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C588">
         <f>100-D588</f>
@@ -18283,15 +18283,15 @@
         <v>1.3785225007599999</v>
       </c>
       <c r="J588" s="7" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="589" spans="1:10" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="589" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B589" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C589">
         <f t="shared" ref="C589:C593" si="49">100-D589</f>
@@ -18315,12 +18315,12 @@
       </c>
       <c r="J589" s="7"/>
     </row>
-    <row r="590" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B590" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C590">
         <f t="shared" si="49"/>
@@ -18344,12 +18344,12 @@
       </c>
       <c r="J590" s="7"/>
     </row>
-    <row r="591" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B591" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C591">
         <f t="shared" si="49"/>
@@ -18373,12 +18373,12 @@
       </c>
       <c r="J591" s="7"/>
     </row>
-    <row r="592" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B592" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C592">
         <f t="shared" si="49"/>
@@ -18402,12 +18402,12 @@
       </c>
       <c r="J592" s="7"/>
     </row>
-    <row r="593" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B593" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C593">
         <f t="shared" si="49"/>
@@ -18431,12 +18431,12 @@
       </c>
       <c r="J593" s="7"/>
     </row>
-    <row r="594" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B594" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C594">
         <v>100</v>
@@ -18458,15 +18458,15 @@
         <v>391.24095645155398</v>
       </c>
       <c r="J594" s="7" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="595" spans="1:10" x14ac:dyDescent="0.25">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="595" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B595" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C595">
         <v>100</v>
@@ -18489,12 +18489,12 @@
       </c>
       <c r="J595" s="7"/>
     </row>
-    <row r="596" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B596" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C596">
         <v>50</v>
@@ -18517,12 +18517,12 @@
       </c>
       <c r="J596" s="7"/>
     </row>
-    <row r="597" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B597" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C597">
         <v>100</v>
@@ -18545,12 +18545,12 @@
       </c>
       <c r="J597" s="7"/>
     </row>
-    <row r="598" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A598" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B598" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C598">
         <v>25</v>
@@ -18573,12 +18573,12 @@
       </c>
       <c r="J598" s="7"/>
     </row>
-    <row r="599" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A599" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B599" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C599">
         <v>25</v>
@@ -18601,12 +18601,12 @@
       </c>
       <c r="J599" s="7"/>
     </row>
-    <row r="600" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A600" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B600" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C600">
         <v>100</v>
@@ -18629,12 +18629,12 @@
       </c>
       <c r="J600" s="7"/>
     </row>
-    <row r="601" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A601" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B601" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C601">
         <v>100</v>
@@ -18657,12 +18657,12 @@
       </c>
       <c r="J601" s="7"/>
     </row>
-    <row r="602" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A602" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B602" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C602">
         <v>50</v>
@@ -18685,12 +18685,12 @@
       </c>
       <c r="J602" s="7"/>
     </row>
-    <row r="603" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A603" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B603" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C603">
         <v>100</v>
@@ -18713,12 +18713,12 @@
       </c>
       <c r="J603" s="7"/>
     </row>
-    <row r="604" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A604" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B604" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C604">
         <v>25</v>
@@ -18741,12 +18741,12 @@
       </c>
       <c r="J604" s="7"/>
     </row>
-    <row r="605" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B605" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C605">
         <v>100</v>
@@ -18769,12 +18769,12 @@
       </c>
       <c r="J605" s="7"/>
     </row>
-    <row r="606" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B606" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C606">
         <v>100</v>
@@ -18799,6 +18799,30 @@
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="J578:J582"/>
+    <mergeCell ref="J583:J587"/>
+    <mergeCell ref="J152:J157"/>
+    <mergeCell ref="J448:J459"/>
+    <mergeCell ref="J158:J169"/>
+    <mergeCell ref="J170:J182"/>
+    <mergeCell ref="J303:J318"/>
+    <mergeCell ref="J319:J332"/>
+    <mergeCell ref="J279:J296"/>
+    <mergeCell ref="J297:J302"/>
+    <mergeCell ref="J183:J220"/>
+    <mergeCell ref="J378:J389"/>
+    <mergeCell ref="J390:J429"/>
+    <mergeCell ref="J430:J436"/>
+    <mergeCell ref="J94:J99"/>
+    <mergeCell ref="J100:J108"/>
+    <mergeCell ref="J109:J118"/>
+    <mergeCell ref="J119:J123"/>
+    <mergeCell ref="J124:J151"/>
+    <mergeCell ref="J2:J17"/>
+    <mergeCell ref="J18:J43"/>
+    <mergeCell ref="J44:J61"/>
+    <mergeCell ref="J62:J65"/>
+    <mergeCell ref="J66:J93"/>
     <mergeCell ref="J588:J593"/>
     <mergeCell ref="J594:J606"/>
     <mergeCell ref="J552:J563"/>
@@ -18815,30 +18839,6 @@
     <mergeCell ref="J533:J551"/>
     <mergeCell ref="J564:J572"/>
     <mergeCell ref="J573:J577"/>
-    <mergeCell ref="J2:J17"/>
-    <mergeCell ref="J18:J43"/>
-    <mergeCell ref="J44:J61"/>
-    <mergeCell ref="J62:J65"/>
-    <mergeCell ref="J66:J93"/>
-    <mergeCell ref="J94:J99"/>
-    <mergeCell ref="J100:J108"/>
-    <mergeCell ref="J109:J118"/>
-    <mergeCell ref="J119:J123"/>
-    <mergeCell ref="J124:J151"/>
-    <mergeCell ref="J578:J582"/>
-    <mergeCell ref="J583:J587"/>
-    <mergeCell ref="J152:J157"/>
-    <mergeCell ref="J448:J459"/>
-    <mergeCell ref="J158:J169"/>
-    <mergeCell ref="J170:J182"/>
-    <mergeCell ref="J303:J318"/>
-    <mergeCell ref="J319:J332"/>
-    <mergeCell ref="J279:J296"/>
-    <mergeCell ref="J297:J302"/>
-    <mergeCell ref="J183:J220"/>
-    <mergeCell ref="J378:J389"/>
-    <mergeCell ref="J390:J429"/>
-    <mergeCell ref="J430:J436"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
